--- a/app/templates/request_template.xlsx
+++ b/app/templates/request_template.xlsx
@@ -1,52 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10110"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{023729E3-40AB-624D-999A-ECCE2162C973}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10201"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vasiliyermolaev/Downloads/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9663C622-F7A6-704F-A141-7634A1D57433}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8840" yWindow="960" windowWidth="34560" windowHeight="17620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Лист1!$A$5:$J$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Лист1!$A$6:$H$6</definedName>
   </definedNames>
-  <calcPr calcId="145621"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
-    <r>
-      <t>Место поставки товаров (выполнения работ, оказания услуг): __</t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="204"/>
-      </rPr>
-      <t>АО «ОЭЗ ППТ «Алабуга»</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="204"/>
-      </rPr>
-      <t>_</t>
-    </r>
+    <t>Подразделение:</t>
+  </si>
+  <si>
+    <t>СПА-салон</t>
+  </si>
+  <si>
+    <t>ЦФО:</t>
+  </si>
+  <si>
+    <t>Коттеджный поселок «Три медведя»</t>
   </si>
   <si>
     <t>Наименование поставляемых товаров, оказываемых услуг, выполняемых работ:</t>
@@ -55,6 +43,9 @@
     <t>Технические и функциональные характеристики товара, работ, услуг,  (потребительские свойства) для определения эквивалентности.</t>
   </si>
   <si>
+    <t>В соответствии с управлением холдингом 1С. (обязательное заполнение в соответствии с Отчетом по лимитам БДДС: Статья ДДС - Товарная категория)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Кол-во </t>
   </si>
   <si>
@@ -64,34 +55,22 @@
     <t>Начально (максимальная) цена договора согласно Плана закупок с НДС в тыс.руб.</t>
   </si>
   <si>
-    <t>Подразделение</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Мол </t>
-  </si>
-  <si>
-    <t>ТЕХНИЧЕСКОЕ ЗАДАНИЕ на 1 квартал 2025г.</t>
-  </si>
-  <si>
-    <t>Ответственный сотрудник ОМТС (Заполняет сотрудник ОМТС)</t>
-  </si>
-  <si>
-    <t>Категория (Заполняет сотрудник ОМТС)</t>
-  </si>
-  <si>
-    <t>Примечание</t>
-  </si>
-  <si>
-    <t>В соответствии с управлением холдингом 1С. (обязательное заполнение в соответствии с Отчетом по лимитам БДДС: Статья ДДС - Товарная категория)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Инициатор закупки продукции (поставки товаров, выполнения работ, оказания услуг):      </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> __________________________</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ЦФО </t>
+    <t>ТЕХНИЧЕСКОЕ ЗАДАНИЕ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Материальноответственное лицо (ФИО полностью) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Примечание </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Место поставки товаров (выполнения работ, оказания услуг): </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Инициатор закупки продукции (поставки товаров, выполнения работ, оказания услуг): </t>
+  </si>
+  <si>
+    <t>АО «ОЭЗ ППТ «Алабуга»</t>
   </si>
 </sst>
 </file>
@@ -101,7 +80,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-419]mmmm;@"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -124,13 +103,6 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-      <charset val="204"/>
-    </font>
-    <font>
-      <u/>
       <sz val="11"/>
       <name val="Times New Roman"/>
       <family val="1"/>
@@ -189,12 +161,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -254,118 +226,118 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
+      <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -652,326 +624,282 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L19"/>
+  <dimension ref="A1:L21"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="15.5" customWidth="1"/>
-    <col min="2" max="2" width="16.6640625" customWidth="1"/>
-    <col min="3" max="3" width="32.1640625" customWidth="1"/>
-    <col min="4" max="4" width="38.5" customWidth="1"/>
-    <col min="5" max="5" width="22.6640625" customWidth="1"/>
-    <col min="7" max="7" width="34.33203125" customWidth="1"/>
-    <col min="8" max="8" width="25.5" customWidth="1"/>
-    <col min="9" max="9" width="17.83203125" customWidth="1"/>
-    <col min="11" max="11" width="16.6640625" customWidth="1"/>
+    <col min="1" max="1" width="24" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="30.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="21.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="42.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="30.5" customWidth="1"/>
+    <col min="10" max="10" width="25.5" customWidth="1"/>
+    <col min="11" max="11" width="16" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="22"/>
+      <c r="J1" s="22"/>
+      <c r="K1" s="23"/>
+      <c r="L1" s="23"/>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="34"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="19"/>
+      <c r="I2" s="23"/>
+      <c r="J2" s="24"/>
+      <c r="K2" s="23"/>
+      <c r="L2" s="23"/>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="27"/>
+      <c r="C3" s="27"/>
+      <c r="D3" s="28"/>
+      <c r="E3" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" s="35"/>
+      <c r="G3" s="36"/>
+      <c r="H3" s="37"/>
+      <c r="I3" s="22"/>
+      <c r="J3" s="22"/>
+      <c r="K3" s="23"/>
+      <c r="L3" s="23"/>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="16"/>
+      <c r="C4" s="16"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="F4" s="38"/>
+      <c r="G4" s="38"/>
+      <c r="H4" s="32"/>
+      <c r="I4" s="22"/>
+      <c r="J4" s="22"/>
+      <c r="K4" s="22"/>
+      <c r="L4" s="22"/>
+    </row>
+    <row r="5" spans="1:12" ht="15" customHeight="1">
+      <c r="A5" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" s="16"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="F5" s="38"/>
+      <c r="G5" s="38"/>
+      <c r="H5" s="32"/>
+      <c r="I5" s="22"/>
+      <c r="J5" s="22"/>
+      <c r="K5" s="22"/>
+      <c r="L5" s="22"/>
+    </row>
+    <row r="6" spans="1:12" ht="52">
+      <c r="A6" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E6" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="22"/>
-      <c r="H1" s="21"/>
-      <c r="I1" s="21"/>
-      <c r="J1" s="21"/>
-      <c r="K1" s="21"/>
-      <c r="L1" s="11"/>
-    </row>
-    <row r="2" spans="1:12">
-      <c r="A2" s="25" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="H2" s="19"/>
-      <c r="I2" s="18"/>
-      <c r="J2" s="18"/>
-      <c r="K2" s="18"/>
-      <c r="L2" s="11"/>
-    </row>
-    <row r="3" spans="1:12">
-      <c r="A3" s="23" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="23"/>
-      <c r="C3" s="23"/>
-      <c r="D3" s="23"/>
-      <c r="E3" s="23"/>
-      <c r="F3" s="23"/>
-      <c r="G3" s="24"/>
-      <c r="H3" s="23"/>
-      <c r="I3" s="23"/>
-      <c r="J3" s="23"/>
-      <c r="K3" s="23"/>
-      <c r="L3" s="11"/>
-    </row>
-    <row r="4" spans="1:12">
-      <c r="A4" s="23"/>
-      <c r="B4" s="23"/>
-      <c r="C4" s="23"/>
-      <c r="D4" s="23"/>
-      <c r="E4" s="23"/>
-      <c r="F4" s="23"/>
-      <c r="G4" s="23"/>
-      <c r="H4" s="23"/>
-      <c r="I4" s="23"/>
-      <c r="J4" s="23"/>
-      <c r="K4" s="23"/>
-      <c r="L4" s="11"/>
-    </row>
-    <row r="5" spans="1:12" ht="81.75" customHeight="1">
-      <c r="A5" s="4" t="s">
+      <c r="F6" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="D5" s="16" t="s">
-        <v>2</v>
-      </c>
-      <c r="E5" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="F5" s="16" t="s">
-        <v>3</v>
-      </c>
-      <c r="G5" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="H5" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="I5" s="16" t="s">
+      <c r="H6" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="J5" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="K5" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="L5" s="16" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
-      <c r="A6" s="11"/>
-      <c r="B6" s="11"/>
-      <c r="C6" s="6"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="11"/>
-      <c r="I6" s="11"/>
-      <c r="J6" s="11"/>
-      <c r="K6" s="11"/>
-      <c r="L6" s="11"/>
     </row>
     <row r="7" spans="1:12">
-      <c r="A7" s="11"/>
-      <c r="B7" s="11"/>
+      <c r="A7" s="14"/>
+      <c r="B7" s="1"/>
       <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="11"/>
-      <c r="I7" s="11"/>
-      <c r="J7" s="11"/>
-      <c r="K7" s="11"/>
-      <c r="L7" s="11"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="30"/>
+      <c r="H7" s="31"/>
     </row>
     <row r="8" spans="1:12">
-      <c r="A8" s="11"/>
-      <c r="B8" s="11"/>
+      <c r="A8" s="14"/>
+      <c r="B8" s="1"/>
       <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="11"/>
-      <c r="J8" s="11"/>
-      <c r="K8" s="11"/>
-      <c r="L8" s="11"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="30"/>
+      <c r="H8" s="31"/>
     </row>
     <row r="9" spans="1:12">
-      <c r="A9" s="11"/>
-      <c r="B9" s="11"/>
+      <c r="A9" s="14"/>
+      <c r="B9" s="1"/>
       <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="11"/>
-      <c r="J9" s="11"/>
-      <c r="K9" s="11"/>
-      <c r="L9" s="11"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="30"/>
+      <c r="H9" s="31"/>
     </row>
     <row r="10" spans="1:12">
-      <c r="A10" s="11"/>
-      <c r="B10" s="11"/>
+      <c r="A10" s="14"/>
+      <c r="B10" s="1"/>
       <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="11"/>
-      <c r="I10" s="11"/>
-      <c r="J10" s="11"/>
-      <c r="K10" s="11"/>
-      <c r="L10" s="11"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="30"/>
+      <c r="H10" s="31"/>
     </row>
     <row r="11" spans="1:12">
-      <c r="A11" s="11"/>
-      <c r="B11" s="11"/>
-      <c r="C11" s="12"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="11"/>
-      <c r="J11" s="11"/>
-      <c r="K11" s="11"/>
-      <c r="L11" s="11"/>
+      <c r="A11" s="14"/>
+      <c r="B11" s="9"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="30"/>
+      <c r="H11" s="31"/>
     </row>
     <row r="12" spans="1:12">
-      <c r="A12" s="11"/>
-      <c r="B12" s="11"/>
+      <c r="A12" s="14"/>
+      <c r="B12" s="1"/>
       <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="11"/>
-      <c r="I12" s="11"/>
-      <c r="J12" s="11"/>
-      <c r="K12" s="11"/>
-      <c r="L12" s="11"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="30"/>
+      <c r="H12" s="31"/>
     </row>
     <row r="13" spans="1:12">
-      <c r="A13" s="11"/>
-      <c r="B13" s="11"/>
-      <c r="C13" s="13"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="11"/>
-      <c r="I13" s="11"/>
-      <c r="J13" s="11"/>
-      <c r="K13" s="11"/>
-      <c r="L13" s="11"/>
+      <c r="A13" s="14"/>
+      <c r="B13" s="10"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="30"/>
+      <c r="H13" s="31"/>
     </row>
     <row r="14" spans="1:12">
-      <c r="A14" s="11"/>
-      <c r="B14" s="11"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="11"/>
-      <c r="I14" s="11"/>
-      <c r="J14" s="11"/>
-      <c r="K14" s="11"/>
-      <c r="L14" s="11"/>
+      <c r="A14" s="14"/>
+      <c r="B14" s="5"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="30"/>
+      <c r="H14" s="31"/>
     </row>
     <row r="15" spans="1:12">
-      <c r="A15" s="11"/>
-      <c r="B15" s="11"/>
-      <c r="C15" s="8"/>
-      <c r="D15" s="1"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="11"/>
-      <c r="I15" s="11"/>
-      <c r="J15" s="11"/>
-      <c r="K15" s="11"/>
-      <c r="L15" s="11"/>
+      <c r="A15" s="14"/>
+      <c r="B15" s="6"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="8"/>
+      <c r="G15" s="30"/>
+      <c r="H15" s="31"/>
     </row>
     <row r="16" spans="1:12">
-      <c r="A16" s="11"/>
-      <c r="B16" s="11"/>
-      <c r="C16" s="13"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-      <c r="H16" s="11"/>
-      <c r="I16" s="11"/>
-      <c r="J16" s="11"/>
-      <c r="K16" s="11"/>
-      <c r="L16" s="11"/>
-    </row>
-    <row r="17" spans="1:12">
-      <c r="A17" s="11"/>
-      <c r="B17" s="11"/>
-      <c r="C17" s="13"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-      <c r="H17" s="11"/>
-      <c r="I17" s="11"/>
-      <c r="J17" s="11"/>
-      <c r="K17" s="11"/>
-      <c r="L17" s="11"/>
-    </row>
-    <row r="18" spans="1:12">
-      <c r="A18" s="11"/>
-      <c r="B18" s="11"/>
+      <c r="A16" s="14"/>
+      <c r="B16" s="10"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="30"/>
+      <c r="H16" s="31"/>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" s="14"/>
+      <c r="B17" s="10"/>
+      <c r="C17" s="11"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="8"/>
+      <c r="G17" s="30"/>
+      <c r="H17" s="31"/>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" s="14"/>
+      <c r="B18" s="1"/>
       <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-      <c r="H18" s="11"/>
-      <c r="I18" s="11"/>
-      <c r="J18" s="11"/>
-      <c r="K18" s="11"/>
-      <c r="L18" s="11"/>
-    </row>
-    <row r="19" spans="1:12">
-      <c r="A19" s="11"/>
-      <c r="B19" s="11"/>
-      <c r="C19" s="1"/>
-      <c r="D19" s="15"/>
-      <c r="E19" s="9"/>
-      <c r="F19" s="10"/>
-      <c r="G19" s="5"/>
-      <c r="H19" s="11"/>
-      <c r="I19" s="11"/>
-      <c r="J19" s="11"/>
-      <c r="K19" s="11"/>
-      <c r="L19" s="11"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="8"/>
+      <c r="G18" s="30"/>
+      <c r="H18" s="31"/>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19" s="14"/>
+      <c r="B19" s="1"/>
+      <c r="C19" s="12"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="8"/>
+      <c r="G19" s="30"/>
+      <c r="H19" s="31"/>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="B21" s="25"/>
+      <c r="C21" s="25"/>
     </row>
   </sheetData>
-  <autoFilter ref="A5:J19" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
-  <mergeCells count="3">
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A3:K4"/>
-    <mergeCell ref="A2:F2"/>
+  <autoFilter ref="A6:H6" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <mergeCells count="9">
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="F4:H4"/>
+    <mergeCell ref="F5:H5"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A5:D5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>